--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2621,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1020"/>
+  <dimension ref="A1:K1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -34329,6 +34329,116 @@
       </c>
       <c r="K1020" s="3" t="inlineStr"/>
     </row>
+    <row r="1021"/>
+    <row r="1022">
+      <c r="A1022" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_MSC_ID_2</t>
+        </is>
+      </c>
+      <c r="B1022" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x703</t>
+        </is>
+      </c>
+      <c r="C1022" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1023" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1023" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1023" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1023" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1023" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1023" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1023" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1023" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1023" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1023" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="3" t="inlineStr">
+        <is>
+          <t>master_runtime</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1024" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1024" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1024" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1024" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1024" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1024" s="3" t="n"/>
+      <c r="I1024" s="3" t="n"/>
+      <c r="J1024" s="3" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="K1024" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2621,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1024"/>
+  <dimension ref="A1:K1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -34439,6 +34439,76 @@
       </c>
       <c r="K1024" s="3" t="inlineStr"/>
     </row>
+    <row r="1025">
+      <c r="A1025" s="3" t="inlineStr">
+        <is>
+          <t>overall_maximum_voltage</t>
+        </is>
+      </c>
+      <c r="B1025" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1025" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1025" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1025" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1025" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1025" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1025" s="3" t="n"/>
+      <c r="I1025" s="3" t="n"/>
+      <c r="J1025" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1025" s="3" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="3" t="inlineStr">
+        <is>
+          <t>overall_maximum_temperature</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1026" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1026" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1026" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1026" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G1026" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1026" s="3" t="n"/>
+      <c r="I1026" s="3" t="n"/>
+      <c r="J1026" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K1026" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -34469,7 +34469,7 @@
       <c r="I1025" s="3" t="n"/>
       <c r="J1025" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t xml:space="preserve"> V</t>
         </is>
       </c>
       <c r="K1025" s="3" t="inlineStr"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -34434,7 +34434,7 @@
       <c r="I1024" s="3" t="n"/>
       <c r="J1024" s="3" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>s</t>
         </is>
       </c>
       <c r="K1024" s="3" t="inlineStr"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2621,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1027"/>
+  <dimension ref="A1:K1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -34474,75 +34474,220 @@
       </c>
       <c r="K1025" s="3" t="inlineStr"/>
     </row>
-    <row r="1026">
-      <c r="A1026" s="3" t="inlineStr">
+    <row r="1026"/>
+    <row r="1027">
+      <c r="A1027" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_MSC_ID_3</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x704</t>
+        </is>
+      </c>
+      <c r="C1027" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1028" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1028" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1028" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1028" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1028" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1028" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1028" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1028" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1028" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1028" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="3" t="inlineStr">
         <is>
           <t>overall_maximum_voltage</t>
         </is>
       </c>
-      <c r="B1026" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C1026" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1026" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E1026" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F1026" s="3" t="n">
+      <c r="B1029" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1029" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1029" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1029" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1029" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="G1026" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1026" s="3" t="n"/>
-      <c r="I1026" s="3" t="n"/>
-      <c r="J1026" s="3" t="inlineStr">
+      <c r="G1029" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1029" s="3" t="n"/>
+      <c r="I1029" s="3" t="n"/>
+      <c r="J1029" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1029" s="3" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="3" t="inlineStr">
+        <is>
+          <t>overall_maximum_temperature</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1030" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1030" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1030" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1030" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G1030" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1030" s="3" t="n"/>
+      <c r="I1030" s="3" t="n"/>
+      <c r="J1030" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K1030" s="3" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="3" t="inlineStr">
+        <is>
+          <t>overall_minimum_voltage</t>
+        </is>
+      </c>
+      <c r="B1031" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1031" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1031" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1031" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1031" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1031" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1031" s="3" t="n"/>
+      <c r="I1031" s="3" t="n"/>
+      <c r="J1031" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> V</t>
         </is>
       </c>
-      <c r="K1026" s="3" t="inlineStr"/>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="3" t="inlineStr">
-        <is>
-          <t>overall_maximum_temperature</t>
-        </is>
-      </c>
-      <c r="B1027" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C1027" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1027" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E1027" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F1027" s="3" t="n">
+      <c r="K1031" s="3" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="3" t="inlineStr">
+        <is>
+          <t>overall_minimum_temperature</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C1032" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1032" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1032" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1032" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G1027" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1027" s="3" t="n"/>
-      <c r="I1027" s="3" t="n"/>
-      <c r="J1027" s="3" t="inlineStr">
+      <c r="G1032" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1032" s="3" t="n"/>
+      <c r="I1032" s="3" t="n"/>
+      <c r="J1032" s="3" t="inlineStr">
         <is>
           <t>ºC</t>
         </is>
       </c>
-      <c r="K1027" s="3" t="inlineStr"/>
+      <c r="K1032" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -5110,7 +5110,7 @@
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t xml:space="preserve"> ºC</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -5110,7 +5110,7 @@
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ºC</t>
+          <t>ºC</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
       <c r="J253" s="3" t="n"/>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No fault detected, 1=Cell/open-wire /voltage diagnostic fault</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2621,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1038"/>
+  <dimension ref="A1:K1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -3496,7 +3496,7 @@
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
@@ -3711,7 +3711,7 @@
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
@@ -3781,7 +3781,7 @@
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
@@ -4250,7 +4250,7 @@
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
@@ -5145,7 +5145,7 @@
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr"/>
@@ -5215,7 +5215,7 @@
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr"/>
@@ -5325,7 +5325,7 @@
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr"/>
@@ -5360,7 +5360,7 @@
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr"/>
@@ -5395,7 +5395,7 @@
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr"/>
@@ -5864,7 +5864,7 @@
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr"/>
@@ -6759,7 +6759,7 @@
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr"/>
@@ -6794,7 +6794,7 @@
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
@@ -6939,7 +6939,7 @@
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr"/>
@@ -6974,7 +6974,7 @@
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr"/>
@@ -7009,7 +7009,7 @@
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr"/>
@@ -8268,7 +8268,7 @@
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr"/>
@@ -8303,7 +8303,7 @@
       <c r="I183" s="3" t="n"/>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr"/>
@@ -8338,7 +8338,7 @@
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr"/>
@@ -8448,7 +8448,7 @@
       <c r="I188" s="3" t="n"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr"/>
@@ -8483,7 +8483,7 @@
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr"/>
@@ -8518,7 +8518,7 @@
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr"/>
@@ -8553,7 +8553,7 @@
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr"/>
@@ -8987,7 +8987,7 @@
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr"/>
@@ -9742,7 +9742,7 @@
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr"/>
@@ -9777,7 +9777,7 @@
       <c r="I231" s="3" t="n"/>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr"/>
@@ -9812,7 +9812,7 @@
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr"/>
@@ -9847,7 +9847,7 @@
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr"/>
@@ -9957,7 +9957,7 @@
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       <c r="I238" s="3" t="n"/>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr"/>
@@ -10027,7 +10027,7 @@
       <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr"/>
@@ -10062,7 +10062,7 @@
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr"/>
@@ -10496,7 +10496,7 @@
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr"/>
@@ -11251,7 +11251,7 @@
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K279" s="3" t="inlineStr"/>
@@ -11286,7 +11286,7 @@
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K280" s="3" t="inlineStr"/>
@@ -11321,7 +11321,7 @@
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr"/>
@@ -11356,7 +11356,7 @@
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K282" s="3" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr"/>
@@ -11501,7 +11501,7 @@
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr"/>
@@ -11536,7 +11536,7 @@
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr"/>
@@ -11571,7 +11571,7 @@
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr"/>
@@ -12005,7 +12005,7 @@
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K303" s="3" t="inlineStr"/>
@@ -12760,7 +12760,7 @@
       <c r="I328" s="3" t="n"/>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K328" s="3" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       <c r="I329" s="3" t="n"/>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K329" s="3" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
       <c r="I330" s="3" t="n"/>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K330" s="3" t="inlineStr"/>
@@ -12865,7 +12865,7 @@
       <c r="I331" s="3" t="n"/>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K331" s="3" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K335" s="3" t="inlineStr"/>
@@ -13010,7 +13010,7 @@
       <c r="I336" s="3" t="n"/>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K336" s="3" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
       <c r="I337" s="3" t="n"/>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K337" s="3" t="inlineStr"/>
@@ -13080,7 +13080,7 @@
       <c r="I338" s="3" t="n"/>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K338" s="3" t="inlineStr"/>
@@ -13514,7 +13514,7 @@
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K352" s="3" t="inlineStr"/>
@@ -14269,7 +14269,7 @@
       <c r="I377" s="3" t="n"/>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K377" s="3" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K378" s="3" t="inlineStr"/>
@@ -14339,7 +14339,7 @@
       <c r="I379" s="3" t="n"/>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K379" s="3" t="inlineStr"/>
@@ -14374,7 +14374,7 @@
       <c r="I380" s="3" t="n"/>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K380" s="3" t="inlineStr"/>
@@ -14484,7 +14484,7 @@
       <c r="I384" s="3" t="n"/>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K384" s="3" t="inlineStr"/>
@@ -14519,7 +14519,7 @@
       <c r="I385" s="3" t="n"/>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K385" s="3" t="inlineStr"/>
@@ -14554,7 +14554,7 @@
       <c r="I386" s="3" t="n"/>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K386" s="3" t="inlineStr"/>
@@ -14589,7 +14589,7 @@
       <c r="I387" s="3" t="n"/>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K387" s="3" t="inlineStr"/>
@@ -15023,7 +15023,7 @@
       <c r="I401" s="3" t="n"/>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K401" s="3" t="inlineStr"/>
@@ -15778,7 +15778,7 @@
       <c r="I426" s="3" t="n"/>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K426" s="3" t="inlineStr"/>
@@ -15813,7 +15813,7 @@
       <c r="I427" s="3" t="n"/>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K427" s="3" t="inlineStr"/>
@@ -15848,7 +15848,7 @@
       <c r="I428" s="3" t="n"/>
       <c r="J428" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K428" s="3" t="inlineStr"/>
@@ -15883,7 +15883,7 @@
       <c r="I429" s="3" t="n"/>
       <c r="J429" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K429" s="3" t="inlineStr"/>
@@ -15993,7 +15993,7 @@
       <c r="I433" s="3" t="n"/>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K433" s="3" t="inlineStr"/>
@@ -16028,7 +16028,7 @@
       <c r="I434" s="3" t="n"/>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K434" s="3" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       <c r="I435" s="3" t="n"/>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K435" s="3" t="inlineStr"/>
@@ -16098,7 +16098,7 @@
       <c r="I436" s="3" t="n"/>
       <c r="J436" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K436" s="3" t="inlineStr"/>
@@ -16532,7 +16532,7 @@
       <c r="I450" s="3" t="n"/>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K450" s="3" t="inlineStr"/>
@@ -17287,7 +17287,7 @@
       <c r="I475" s="3" t="n"/>
       <c r="J475" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K475" s="3" t="inlineStr"/>
@@ -17322,7 +17322,7 @@
       <c r="I476" s="3" t="n"/>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K476" s="3" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       <c r="I477" s="3" t="n"/>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K477" s="3" t="inlineStr"/>
@@ -17392,7 +17392,7 @@
       <c r="I478" s="3" t="n"/>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K478" s="3" t="inlineStr"/>
@@ -17502,7 +17502,7 @@
       <c r="I482" s="3" t="n"/>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K482" s="3" t="inlineStr"/>
@@ -17537,7 +17537,7 @@
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K483" s="3" t="inlineStr"/>
@@ -17572,7 +17572,7 @@
       <c r="I484" s="3" t="n"/>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K484" s="3" t="inlineStr"/>
@@ -17607,7 +17607,7 @@
       <c r="I485" s="3" t="n"/>
       <c r="J485" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K485" s="3" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       <c r="I499" s="3" t="n"/>
       <c r="J499" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr"/>
@@ -18796,7 +18796,7 @@
       <c r="I524" s="3" t="n"/>
       <c r="J524" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K524" s="3" t="inlineStr"/>
@@ -18831,7 +18831,7 @@
       <c r="I525" s="3" t="n"/>
       <c r="J525" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K525" s="3" t="inlineStr"/>
@@ -18866,7 +18866,7 @@
       <c r="I526" s="3" t="n"/>
       <c r="J526" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K526" s="3" t="inlineStr"/>
@@ -18901,7 +18901,7 @@
       <c r="I527" s="3" t="n"/>
       <c r="J527" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K527" s="3" t="inlineStr"/>
@@ -19011,7 +19011,7 @@
       <c r="I531" s="3" t="n"/>
       <c r="J531" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K531" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       <c r="I532" s="3" t="n"/>
       <c r="J532" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K532" s="3" t="inlineStr"/>
@@ -19081,7 +19081,7 @@
       <c r="I533" s="3" t="n"/>
       <c r="J533" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K533" s="3" t="inlineStr"/>
@@ -19116,7 +19116,7 @@
       <c r="I534" s="3" t="n"/>
       <c r="J534" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K534" s="3" t="inlineStr"/>
@@ -19550,7 +19550,7 @@
       <c r="I548" s="3" t="n"/>
       <c r="J548" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K548" s="3" t="inlineStr"/>
@@ -20305,7 +20305,7 @@
       <c r="I573" s="3" t="n"/>
       <c r="J573" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K573" s="3" t="inlineStr"/>
@@ -20340,7 +20340,7 @@
       <c r="I574" s="3" t="n"/>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K574" s="3" t="inlineStr"/>
@@ -20375,7 +20375,7 @@
       <c r="I575" s="3" t="n"/>
       <c r="J575" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K575" s="3" t="inlineStr"/>
@@ -20410,7 +20410,7 @@
       <c r="I576" s="3" t="n"/>
       <c r="J576" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K576" s="3" t="inlineStr"/>
@@ -20520,7 +20520,7 @@
       <c r="I580" s="3" t="n"/>
       <c r="J580" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K580" s="3" t="inlineStr"/>
@@ -20555,7 +20555,7 @@
       <c r="I581" s="3" t="n"/>
       <c r="J581" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K581" s="3" t="inlineStr"/>
@@ -20590,7 +20590,7 @@
       <c r="I582" s="3" t="n"/>
       <c r="J582" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K582" s="3" t="inlineStr"/>
@@ -20625,7 +20625,7 @@
       <c r="I583" s="3" t="n"/>
       <c r="J583" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K583" s="3" t="inlineStr"/>
@@ -21059,7 +21059,7 @@
       <c r="I597" s="3" t="n"/>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K597" s="3" t="inlineStr"/>
@@ -21204,7 +21204,7 @@
       <c r="I602" s="3" t="n"/>
       <c r="J602" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K602" s="3" t="inlineStr"/>
@@ -34824,7 +34824,7 @@
       <c r="I1036" s="3" t="n"/>
       <c r="J1036" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K1036" s="3" t="inlineStr"/>
@@ -34894,10 +34894,124 @@
       <c r="I1038" s="3" t="n"/>
       <c r="J1038" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K1038" s="3" t="inlineStr"/>
+    </row>
+    <row r="1039"/>
+    <row r="1040">
+      <c r="A1040" s="1" t="inlineStr">
+        <is>
+          <t>Message: Start_Balancing</t>
+        </is>
+      </c>
+      <c r="B1040" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x84</t>
+        </is>
+      </c>
+      <c r="C1040" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1041" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1041" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1041" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1041" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1041" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1041" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1041" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1041" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="3" t="inlineStr">
+        <is>
+          <t>Balancing_Request</t>
+        </is>
+      </c>
+      <c r="B1042" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1042" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1042" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1042" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1042" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1042" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1042" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1042" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1042" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K1042" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -34908,7 +34908,7 @@
       </c>
       <c r="B1040" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x84</t>
+          <t>ID: 0x82</t>
         </is>
       </c>
       <c r="C1040" s="1" t="inlineStr">
